--- a/public/share/data/论文数据清单.xlsx
+++ b/public/share/data/论文数据清单.xlsx
@@ -2,57 +2,218 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="采集清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="研究问题" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="27">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="PingFang SC"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="PingFang SC"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="PingFang SC"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="PingFang SC"/>
+      <charset val="134"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+      <color rgb="FF228B22"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="PingFang SC"/>
-      <color rgb="00228B22"/>
-      <sz val="11"/>
+      <charset val="134"/>
+      <color rgb="FF228B22"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill/>
     </fill>
@@ -61,18 +222,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C3E50"/>
-        <bgColor rgb="002C3E50"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E3F2FD"/>
-        <bgColor rgb="00E3F2FD"/>
+        <fgColor rgb="FF2C3E50"/>
+        <bgColor rgb="FF2C3E50"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+        <bgColor rgb="FFE3F2FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -82,23 +429,181 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -106,67 +611,252 @@
     <border>
       <left/>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="FFD0D0D0"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D0D0D0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D0D0D0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D0D0D0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="14" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -519,7 +1209,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -529,354 +1218,350 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30.4519230769231" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>论文数据采集清单</t>
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>采集项</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>在哪</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>什么时候填</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  📋 日常采集（每天）</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>晨间问卷</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>每日监控</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>训练日每人 5题×1-5</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>✅ 7/6-13 8天 23-29人/天</t>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>✅ 7/6-8/13 覆盖全部训练日（35天+）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>sRPE</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>每日监控</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>训练/比赛后 RPE×时长</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>✅ 7/6-12 7天训练日完整</t>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>✅ 7/6-8/13 训练日sRPE完整</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>训练课记录</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>训练课记录</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>练习名称+时长+执行度</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>✅ 7/6-13 8天完整</t>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>✅ 7/6-8/13 完整</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  ⚽ 比赛（每场）</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="10" t="n"/>
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="15" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>比赛记录</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>比赛记录</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>每场每人 出场/RPE/sRPE</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>✅ 7/8 vs大连可为 2-0</t>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>✅ 6场已记录：7/8、7/19、7/26、8/1、8/5、8/9</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>伤病记录</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>伤病与体测</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>发生即记</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>✅ 6人伤病记录完整</t>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>✅ 持续记录·含8/13张俊哲脚微痛/艾沙江左后群紧</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  🧪 体测（赛季3次）</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="15" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Yo-Yo IR1</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>伤病与体测</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>间歇期体测</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>⬜ 8月</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>10m+30m冲刺</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>伤病与体测</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>间歇期体测</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>CMJ</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>每日监控/体测</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>每周1次+体测日</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>体脂%</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>伤病与体测</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>间歇期体测</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  🤖 AI系统（每课）</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10" t="n"/>
+      <c r="B16" s="14" t="n"/>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="15" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>方案ID+执行度</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>训练课记录</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>L+M列</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>⬜ M2启动</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>教练调整理由</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>训练课记录</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>N列 定性文本</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>⬜</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">  📊 填日志（每周）</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="15" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>平台使用日志</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>平台使用日志</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>M1-M16 6模块评分+反思</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>🟡 M1部分</t>
         </is>
@@ -884,9 +1569,9 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A16:D16"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A19:D19"/>
@@ -902,14 +1587,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="20.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>7个研究问题</t>
@@ -934,119 +1619,119 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Q1 可行性</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>AI方案在中乙能落地吗？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>执行率≥60%即证明可行</t>
         </is>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Q2 偏差</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>AI计划 vs 实际执行的差距</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>配对t检验 看偏差集中在哪类训练</t>
         </is>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Q3 教练判断 ⭐</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>教练为什么改AI方案？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>定性分析 归纳3-5个核心主题 论文最值钱的部分</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Q4 效果</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>AI辅助后体能有没有改善？</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>季前→季中→季末体测对比 超过SWC才算有意义</t>
         </is>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Q5 依从</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>球员填不填问卷？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>填写率&gt;80%可接受</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Q6 负荷</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>AI方案的ACWR在安全窗内吗？</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>落在0.8-1.3的比例 引用Gabbett 2016</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Q7 方法 ⭐</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>零硬件采集体系本身可行吗？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>方法论贡献 低资源环境能做什么不能做什么</t>
         </is>
